--- a/0.0 - Infrastructure around coding - VS Code/1.01 - Proposed Map.xlsx
+++ b/0.0 - Infrastructure around coding - VS Code/1.01 - Proposed Map.xlsx
@@ -1,31 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ellio\Documents\Documents - Python\A beginners guide to Python\0.0 - Infrastructure around coding - VS Code\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ellio\Documents\Python\A beginners guide to Python\0.0 - Infrastructure around coding - VS Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C3688D-0C8F-4531-BA2A-1D5F3D3D7850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0EA71E6-6EE8-4D19-95F7-A60FC1237605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="21900" windowHeight="25296" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="4.0 - Codeacademy" sheetId="4" r:id="rId1"/>
+    <sheet name="1.01 - Proposed map" sheetId="1" r:id="rId2"/>
+    <sheet name="Rankings" sheetId="5" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="135">
   <si>
     <t>Dipping the toe</t>
   </si>
@@ -124,13 +137,322 @@
   </si>
   <si>
     <t>1.24 - Parial functions</t>
+  </si>
+  <si>
+    <t>Topics covered</t>
+  </si>
+  <si>
+    <t>1. 4.01 - Comments.py</t>
+  </si>
+  <si>
+    <t>Learned Python comments and basic print() output.</t>
+  </si>
+  <si>
+    <t>2. 4.02 - Errors &amp; arithmetic.py</t>
+  </si>
+  <si>
+    <t>Learned to fix syntax errors, arithmetic operations, modulo, float vs integer division, type conversion, and formatted print output.</t>
+  </si>
+  <si>
+    <t>Also touched on datetime.strptime() parsing and datetime usage.</t>
+  </si>
+  <si>
+    <t>3. 4.03 - Tip calculator.py</t>
+  </si>
+  <si>
+    <t>Learned basic math for tip/tax calculations.</t>
+  </si>
+  <si>
+    <t>Learned string handling: indexing, len(), .lower(), .upper(), and concatenation/formatting.</t>
+  </si>
+  <si>
+    <t>4. 4.04 - Date and time.py</t>
+  </si>
+  <si>
+    <t>Learned datetime.now(), date/time formatting, and output formatting with %02d/%04d.</t>
+  </si>
+  <si>
+    <t>5. 4.05 - Python Mad Libs.py</t>
+  </si>
+  <si>
+    <t>Learned user input collection and string templating with % substitution for a Mad Libs story.</t>
+  </si>
+  <si>
+    <t>6. 4.06 -Conditionals and control flow.py</t>
+  </si>
+  <si>
+    <t>Learned if / elif / else, input handling, and branching logic for choices.</t>
+  </si>
+  <si>
+    <t>7. 4.07 - PygLatin.py</t>
+  </si>
+  <si>
+    <t>Learned string manipulation and simple algorithmic transformation for Pig Latin.</t>
+  </si>
+  <si>
+    <t>Learned input validation and conditional flow.</t>
+  </si>
+  <si>
+    <t>8. 4.08 - Functions.py</t>
+  </si>
+  <si>
+    <t>Learned function definition with def, docstrings, function calling, and returning values.</t>
+  </si>
+  <si>
+    <t>9. 4.09 - Lists and dictionaries.py</t>
+  </si>
+  <si>
+    <t>Learned list operations, dictionary operations, indexing, and basic data structure usage.</t>
+  </si>
+  <si>
+    <t>10. 4.10 - For loops (supermarket).py</t>
+  </si>
+  <si>
+    <t>Learned for loops, iterating over lists, and using functions to compute totals.</t>
+  </si>
+  <si>
+    <t>11. 4.11 - Dictionaries and lists.py</t>
+  </si>
+  <si>
+    <t>Learned nested data structures: lists of dictionaries, grade calculation, and more structured data handling.</t>
+  </si>
+  <si>
+    <t>12. 4.12 - List accessing.py</t>
+  </si>
+  <si>
+    <t>Learned list indexing, list mutation, and helper functions for list processing.</t>
+  </si>
+  <si>
+    <t>13. 4.13 - Battleships.py</t>
+  </si>
+  <si>
+    <t>Learned how to build a grid with nested lists, use loops and conditionals for game logic, and handle user input in a small game.</t>
+  </si>
+  <si>
+    <t>14. 4.14 - Loops.py</t>
+  </si>
+  <si>
+    <t>Learned loop and conditional interaction, including for / while style control flow and break-style logic.</t>
+  </si>
+  <si>
+    <t>15. 4.15 - Practise makes perfect.py</t>
+  </si>
+  <si>
+    <t>Learned function-based problem solving: even/odd checks, integer checks, digit sums, factorials, prime testing, string reversal, anti-vowel filtering, Scrabble scoring, and censoring text.</t>
+  </si>
+  <si>
+    <t>16. 4.16 - Exam statistics.py</t>
+  </si>
+  <si>
+    <t>Learned list-based statistics: average, variance, and standard deviation.</t>
+  </si>
+  <si>
+    <t>17. 4.17 - Advanced topics.py</t>
+  </si>
+  <si>
+    <t>Learned dictionary iteration (.items(), .keys(), .values()), list comprehensions, slicing, filter(), anonymous lambda functions, and using next() with iterators.</t>
+  </si>
+  <si>
+    <t>18. 4.18 - Bitwise operators.py</t>
+  </si>
+  <si>
+    <t>Learned bitwise operators: &lt;&lt;, &gt;&gt;, &amp;, |, ^, ~, binary literals (0b...), bin(), and bit masking/testing.</t>
+  </si>
+  <si>
+    <t>19. 4.19 - Introduction to classes.py</t>
+  </si>
+  <si>
+    <t>Learned object-oriented basics: class concepts, attributes, methods, and instance creation.</t>
+  </si>
+  <si>
+    <t>20. 4.20 - Class basics.py</t>
+  </si>
+  <si>
+    <t>Learned class constructors (__init__), object state, and class methods with a Car example.</t>
+  </si>
+  <si>
+    <t>21. 4.21 - File input and output.py</t>
+  </si>
+  <si>
+    <t>Learned file I/O: opening files, writing, reading, with/as, buffering, readline(), split(), and checking file closed state.</t>
+  </si>
+  <si>
+    <t>4.01 - Comments</t>
+  </si>
+  <si>
+    <t>4.02 - Errors and arithmetic</t>
+  </si>
+  <si>
+    <t>4.04 - Date and time</t>
+  </si>
+  <si>
+    <t>4.06 - Conditionals and control flow</t>
+  </si>
+  <si>
+    <t>4.08 - Functions</t>
+  </si>
+  <si>
+    <t>4.09 - Lists and dictionaries</t>
+  </si>
+  <si>
+    <t>4.10 - For loops</t>
+  </si>
+  <si>
+    <t>4.11 - Dictionaries and lists</t>
+  </si>
+  <si>
+    <t>4.12 - List accessing</t>
+  </si>
+  <si>
+    <t>4.19 - Introduction to classes</t>
+  </si>
+  <si>
+    <t>4.20 - Class basics</t>
+  </si>
+  <si>
+    <t>4.02 - Errors and arithmetic</t>
+  </si>
+  <si>
+    <t>4.04 - Date and time</t>
+  </si>
+  <si>
+    <t>4.05 - Input and string templating</t>
+  </si>
+  <si>
+    <t>4.06 - Conditionals and control flow</t>
+  </si>
+  <si>
+    <t>4.07 - String transformation</t>
+  </si>
+  <si>
+    <t>4.08 - Functions</t>
+  </si>
+  <si>
+    <t>4.09 - Lists and dictionaries</t>
+  </si>
+  <si>
+    <t>4.10 - For loops</t>
+  </si>
+  <si>
+    <t>4.11 - Dictionaries and lists</t>
+  </si>
+  <si>
+    <t>4.12 - List accessing</t>
+  </si>
+  <si>
+    <t>4.13 - Nested lists and board logic</t>
+  </si>
+  <si>
+    <t>4.14 - Loops and branching</t>
+  </si>
+  <si>
+    <t>4.15 - Practice algorithms</t>
+  </si>
+  <si>
+    <t>4.16 - Statistics with lists</t>
+  </si>
+  <si>
+    <t>4.17 - Advanced iterables and lambdas</t>
+  </si>
+  <si>
+    <t>4.18 - Bitwise operators</t>
+  </si>
+  <si>
+    <t>4.19 - Introduction to classes</t>
+  </si>
+  <si>
+    <t>4.20 - Class basics</t>
+  </si>
+  <si>
+    <t>4.21 - File input/output</t>
+  </si>
+  <si>
+    <t>4.03 - String manipulation</t>
+  </si>
+  <si>
+    <t>4.01 - Hello World</t>
+  </si>
+  <si>
+    <t>LearnPython.org</t>
+  </si>
+  <si>
+    <t>Sololearn (Free)</t>
+  </si>
+  <si>
+    <t>Python Introduction</t>
+  </si>
+  <si>
+    <t>Context &amp; Relevance</t>
+  </si>
+  <si>
+    <t>Course Structure</t>
+  </si>
+  <si>
+    <t>Content Quality</t>
+  </si>
+  <si>
+    <t>Flow &amp; Interactivity</t>
+  </si>
+  <si>
+    <t>Pacing</t>
+  </si>
+  <si>
+    <t>Production &amp; Medium</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Codecademy</t>
+  </si>
+  <si>
+    <t>Je ne sais quoi / 5</t>
+  </si>
+  <si>
+    <t>4.03 - Tip calculator / string manipulation</t>
+  </si>
+  <si>
+    <t>4.05 - Input and string templating</t>
+  </si>
+  <si>
+    <t>4.07 - String transformation</t>
+  </si>
+  <si>
+    <t>4.13 - Nested lists and board logic</t>
+  </si>
+  <si>
+    <t>4.14 - Loops and branching</t>
+  </si>
+  <si>
+    <t>4.15 - Practice algorithms</t>
+  </si>
+  <si>
+    <t>4.16 - Statistics with lists</t>
+  </si>
+  <si>
+    <t>4.17 - Advanced iterables and lambdas</t>
+  </si>
+  <si>
+    <t>4.18 - Bitwise operators</t>
+  </si>
+  <si>
+    <t>4.21 - File input/output</t>
+  </si>
+  <si>
+    <t>Average</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="177" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -166,16 +488,53 @@
       <name val="Aptos Light"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.14999847407452621"/>
+      <name val="Aptos Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Light"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7FFE7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF5F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -213,11 +572,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -225,12 +613,49 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFF20057"/>
+      <color rgb="FFFFD636"/>
+      <color rgb="FF8252DE"/>
+      <color rgb="FF204056"/>
+      <color rgb="FFFEF5F0"/>
+      <color rgb="FFE7FFE7"/>
+      <color rgb="FFFBFFFB"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -240,6 +665,1256 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Rankings!$C$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>LearnPython.org</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFD636"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Rankings!$B$6:$B$12</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Context &amp; Relevance</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Course Structure</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Content Quality</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Flow &amp; Interactivity</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Pacing</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Production &amp; Medium</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Value</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Rankings!$C$6:$C$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D03C-45D4-B1EF-45A83EFC4AE0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Rankings!$D$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sololearn (Free)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="F20057"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Rankings!$B$6:$B$12</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Context &amp; Relevance</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Course Structure</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Content Quality</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Flow &amp; Interactivity</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Pacing</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Production &amp; Medium</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Value</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Rankings!$D$6:$D$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D03C-45D4-B1EF-45A83EFC4AE0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Rankings!$E$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Codecademy</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="204056"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Rankings!$B$6:$B$12</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Context &amp; Relevance</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Course Structure</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Content Quality</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Flow &amp; Interactivity</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Pacing</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Production &amp; Medium</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Value</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Rankings!$E$6:$E$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-D03C-45D4-B1EF-45A83EFC4AE0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Rankings!$F$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Average</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="bg1">
+                <a:lumMod val="95000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Rankings!$B$6:$B$12</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Context &amp; Relevance</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Course Structure</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Content Quality</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Flow &amp; Interactivity</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Pacing</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Production &amp; Medium</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Value</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Rankings!$F$6:$F$12</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>2.6666666666666665</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.333333333333333</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.666666666666667</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.333333333333333</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.666666666666667</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-D03C-45D4-B1EF-45A83EFC4AE0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="756081535"/>
+        <c:axId val="756068095"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="756081535"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="756068095"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="756068095"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="756081535"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>34290</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>49530</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E7AC425-A848-B809-BD90-651605C50555}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -504,16 +2179,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A4:M38"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15B86D8A-CBC0-49C9-9806-C0813A4AC871}">
+  <dimension ref="A4:M78"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="24.85546875" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="24.88671875" customWidth="1"/>
     <col min="7" max="7" width="9" customWidth="1"/>
+    <col min="10" max="10" width="36.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -522,7 +2199,7 @@
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -531,7 +2208,7 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
-    <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2"/>
       <c r="B6" s="3" t="s">
         <v>0</v>
@@ -544,7 +2221,7 @@
       <c r="F6" s="4"/>
       <c r="G6" s="2"/>
     </row>
-    <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2"/>
       <c r="B7" s="3"/>
       <c r="C7" s="4"/>
@@ -554,8 +2231,11 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2"/>
       <c r="B8" s="3"/>
       <c r="C8" s="4"/>
@@ -566,7 +2246,7 @@
       <c r="F8" s="4"/>
       <c r="G8" s="2"/>
     </row>
-    <row r="9" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2"/>
       <c r="B9" s="3"/>
       <c r="C9" s="4"/>
@@ -576,8 +2256,11 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" s="4"/>
@@ -586,7 +2269,7 @@
       <c r="F10" s="4"/>
       <c r="G10" s="2"/>
     </row>
-    <row r="11" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2"/>
       <c r="B11" s="3"/>
       <c r="C11" s="4"/>
@@ -594,8 +2277,11 @@
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2"/>
       <c r="B12" s="3"/>
       <c r="C12" s="4"/>
@@ -609,8 +2295,11 @@
         <v>7</v>
       </c>
       <c r="G12" s="5"/>
-    </row>
-    <row r="13" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2"/>
       <c r="B13" s="3"/>
       <c r="C13" s="4"/>
@@ -619,7 +2308,7 @@
       <c r="F13" s="4"/>
       <c r="G13" s="2"/>
     </row>
-    <row r="14" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2"/>
       <c r="B14" s="3" t="s">
         <v>5</v>
@@ -631,8 +2320,11 @@
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2"/>
       <c r="B15" s="3"/>
       <c r="C15" s="4"/>
@@ -642,8 +2334,11 @@
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2"/>
       <c r="B16" s="3"/>
       <c r="C16" s="4"/>
@@ -653,8 +2348,11 @@
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2"/>
       <c r="B17" s="3"/>
       <c r="C17" s="4"/>
@@ -665,7 +2363,7 @@
       <c r="F17" s="4"/>
       <c r="G17" s="2"/>
     </row>
-    <row r="18" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -675,8 +2373,11 @@
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2"/>
       <c r="B19" s="3"/>
       <c r="C19" s="4"/>
@@ -686,8 +2387,11 @@
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M19" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2"/>
       <c r="B20" s="6" t="s">
         <v>13</v>
@@ -699,8 +2403,11 @@
         <v>27</v>
       </c>
       <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -711,7 +2418,7 @@
       <c r="F21" s="4"/>
       <c r="G21" s="2"/>
     </row>
-    <row r="22" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2"/>
       <c r="B22" s="3"/>
       <c r="C22" s="4"/>
@@ -721,8 +2428,11 @@
       </c>
       <c r="F22" s="4"/>
       <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M22" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2"/>
       <c r="B23" s="3"/>
       <c r="C23" s="4"/>
@@ -732,8 +2442,11 @@
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M23" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -744,7 +2457,7 @@
       <c r="F24" s="4"/>
       <c r="G24" s="2"/>
     </row>
-    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -754,8 +2467,11 @@
       </c>
       <c r="F25" s="4"/>
       <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2"/>
       <c r="B26" s="3" t="s">
         <v>18</v>
@@ -767,8 +2483,11 @@
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M26" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -779,7 +2498,7 @@
       <c r="F27" s="4"/>
       <c r="G27" s="2"/>
     </row>
-    <row r="28" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -787,8 +2506,11 @@
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="2"/>
-    </row>
-    <row r="29" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M28" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -798,8 +2520,11 @@
         <v>25</v>
       </c>
       <c r="G29" s="2"/>
-    </row>
-    <row r="30" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M29" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -810,7 +2535,7 @@
       </c>
       <c r="G30" s="2"/>
     </row>
-    <row r="31" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -820,8 +2545,11 @@
         <v>26</v>
       </c>
       <c r="G31" s="2"/>
-    </row>
-    <row r="32" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M31" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -831,8 +2559,11 @@
       </c>
       <c r="F32" s="4"/>
       <c r="G32" s="2"/>
-    </row>
-    <row r="33" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M32" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -842,8 +2573,11 @@
       </c>
       <c r="F33" s="4"/>
       <c r="G33" s="2"/>
-    </row>
-    <row r="34" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M33" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -853,9 +2587,8 @@
       </c>
       <c r="F34" s="4"/>
       <c r="G34" s="2"/>
-      <c r="M34" s="1"/>
-    </row>
-    <row r="35" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -865,8 +2598,11 @@
       </c>
       <c r="F35" s="4"/>
       <c r="G35" s="2"/>
-    </row>
-    <row r="36" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M35" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
@@ -876,8 +2612,11 @@
       </c>
       <c r="F36" s="4"/>
       <c r="G36" s="2"/>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M36" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -886,7 +2625,7 @@
       <c r="F37" s="4"/>
       <c r="G37" s="2"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -894,8 +2633,1237 @@
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
+      <c r="M38" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M39" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="M41" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="M42" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+    </row>
+    <row r="44" spans="1:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B44" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C44" s="4"/>
+      <c r="D44" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="M44" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B45" s="3"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E45" s="4"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="M45" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B46" s="3"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B47" s="3"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="F47" s="4"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="M47" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B48" s="3"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="M48" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="49" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B49" s="3"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="50" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B50" s="3"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="M50" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="51" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B51" s="3"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="M51" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="52" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C52" s="4"/>
+      <c r="D52" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E52" s="4"/>
+      <c r="F52" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="53" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B53" s="3"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="M53" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="54" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B54" s="3"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F54" s="4"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="M54" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="55" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B55" s="3"/>
+      <c r="C55" s="4"/>
+      <c r="E55" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="F55" s="4"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="56" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F56" s="4"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="M56" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="57" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E57" s="4"/>
+      <c r="F57" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="58" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B58" s="3"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="M58" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="59" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B59" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C59" s="4"/>
+      <c r="D59" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E59" s="4"/>
+      <c r="F59" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="60" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F60" s="4"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="M60" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="61" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B61" s="3"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F61" s="4"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="M61" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="62" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B62" s="3"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F62" s="9"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="63" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B63" s="3"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="64" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B64" s="3"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+      <c r="I64" s="2"/>
+      <c r="J64" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F65" s="4"/>
+      <c r="G65" s="2"/>
+      <c r="I65" s="2"/>
+      <c r="M65" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F66" s="4"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
+      <c r="M66" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B67" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F67" s="4"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+      <c r="J67" s="2"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F68" s="4"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="M68" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+      <c r="J69" s="2"/>
+      <c r="M69" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+      <c r="J70" s="2"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+      <c r="J71" s="2"/>
+      <c r="M71" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+      <c r="J72" s="2"/>
+      <c r="M72" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B73" s="4"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="4"/>
+      <c r="E73" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F73" s="4"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
+      <c r="J73" s="2"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F74" s="4"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+      <c r="I74" s="2"/>
+      <c r="J74" s="2"/>
+      <c r="M74" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
+      <c r="E75" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F75" s="4"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+      <c r="I75" s="2"/>
+      <c r="J75" s="2"/>
+      <c r="M75" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B76" s="4"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F76" s="4"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
+      <c r="J76" s="2"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F77" s="4"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+      <c r="I77" s="2"/>
+      <c r="J77" s="2"/>
+      <c r="M77" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="78" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B78" s="4"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
+      <c r="I78" s="2"/>
+      <c r="J78" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A4:M38"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="24.88671875" customWidth="1"/>
+    <col min="7" max="7" width="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2"/>
+      <c r="B6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="5"/>
+    </row>
+    <row r="13" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2"/>
+      <c r="B14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="2"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="4"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="2"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2"/>
+      <c r="B20" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" s="4"/>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="2"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="4"/>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="2"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="2"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="2"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25" s="4"/>
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="2"/>
+      <c r="B26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F26" s="4"/>
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="2"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F27" s="4"/>
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="2"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="2"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="2"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G30" s="2"/>
+    </row>
+    <row r="31" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="2"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="2"/>
+    </row>
+    <row r="32" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F32" s="4"/>
+      <c r="G32" s="2"/>
+    </row>
+    <row r="33" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F33" s="4"/>
+      <c r="G33" s="2"/>
+    </row>
+    <row r="34" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="2"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F34" s="4"/>
+      <c r="G34" s="2"/>
+      <c r="M34" s="1"/>
+    </row>
+    <row r="35" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="2"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F35" s="4"/>
+      <c r="G35" s="2"/>
+    </row>
+    <row r="36" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="2"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F36" s="4"/>
+      <c r="G36" s="2"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A37" s="2"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="2"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13940C03-9827-4469-8494-BEBDFCC1DD08}">
+  <dimension ref="B3:F14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="18.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D3" s="12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C5" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="C6" s="12">
+        <v>2</v>
+      </c>
+      <c r="D6" s="12">
+        <v>3</v>
+      </c>
+      <c r="E6" s="12">
+        <v>3</v>
+      </c>
+      <c r="F6" s="18">
+        <f>AVERAGE(C6:E6)</f>
+        <v>2.6666666666666665</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B7" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" s="12">
+        <v>5</v>
+      </c>
+      <c r="D7" s="12">
+        <v>7</v>
+      </c>
+      <c r="E7" s="12">
+        <v>4</v>
+      </c>
+      <c r="F7" s="18">
+        <f t="shared" ref="F7:F14" si="0">AVERAGE(C7:E7)</f>
+        <v>5.333333333333333</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B8" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="C8" s="12">
+        <v>9</v>
+      </c>
+      <c r="D8" s="12">
+        <v>4</v>
+      </c>
+      <c r="E8" s="12">
+        <v>5</v>
+      </c>
+      <c r="F8" s="18">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B9" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" s="12">
+        <v>6</v>
+      </c>
+      <c r="D9" s="12">
+        <v>4</v>
+      </c>
+      <c r="E9" s="12">
+        <v>4</v>
+      </c>
+      <c r="F9" s="18">
+        <f t="shared" si="0"/>
+        <v>4.666666666666667</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B10" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="C10" s="12">
+        <v>6</v>
+      </c>
+      <c r="D10" s="12">
+        <v>7</v>
+      </c>
+      <c r="E10" s="12">
+        <v>6</v>
+      </c>
+      <c r="F10" s="18">
+        <f t="shared" si="0"/>
+        <v>6.333333333333333</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B11" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" s="12">
+        <v>5</v>
+      </c>
+      <c r="D11" s="12">
+        <v>7</v>
+      </c>
+      <c r="E11" s="12">
+        <v>5</v>
+      </c>
+      <c r="F11" s="18">
+        <f t="shared" si="0"/>
+        <v>5.666666666666667</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B12" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" s="12">
+        <v>8</v>
+      </c>
+      <c r="D12" s="12">
+        <v>5</v>
+      </c>
+      <c r="E12" s="12">
+        <v>5</v>
+      </c>
+      <c r="F12" s="18">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" s="14">
+        <v>2</v>
+      </c>
+      <c r="D13" s="14">
+        <v>1</v>
+      </c>
+      <c r="E13" s="14">
+        <v>0</v>
+      </c>
+      <c r="F13" s="19">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="C14" s="13">
+        <v>43</v>
+      </c>
+      <c r="D14" s="13">
+        <v>38</v>
+      </c>
+      <c r="E14" s="13">
+        <f>SUM(E6:E13)</f>
+        <v>32</v>
+      </c>
+      <c r="F14" s="20">
+        <f t="shared" si="0"/>
+        <v>37.666666666666664</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C6:E12">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6:F12">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/0.0 - Infrastructure around coding - VS Code/1.01 - Proposed Map.xlsx
+++ b/0.0 - Infrastructure around coding - VS Code/1.01 - Proposed Map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ellio\Documents\Python\A beginners guide to Python\0.0 - Infrastructure around coding - VS Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0EA71E6-6EE8-4D19-95F7-A60FC1237605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48AE0EB1-B3D0-4316-84B7-B67B51695617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="21900" windowHeight="25296" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3372" windowWidth="26004" windowHeight="21924" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="4.0 - Codeacademy" sheetId="4" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="142">
   <si>
     <t>Dipping the toe</t>
   </si>
@@ -443,6 +443,27 @@
   </si>
   <si>
     <t>Average</t>
+  </si>
+  <si>
+    <t>Out of place items</t>
+  </si>
+  <si>
+    <t>Key:</t>
+  </si>
+  <si>
+    <t>New subjects</t>
+  </si>
+  <si>
+    <t>Repeated subjects</t>
+  </si>
+  <si>
+    <t>Non-repeated subjects</t>
+  </si>
+  <si>
+    <t>Subjects covered twice</t>
+  </si>
+  <si>
+    <t>Covered but with a different name</t>
   </si>
 </sst>
 </file>
@@ -450,9 +471,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -507,8 +528,14 @@
       <name val="Aptos Light"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Light"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -533,8 +560,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF204056"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -601,11 +634,108 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -615,7 +745,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -630,15 +760,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -647,10 +788,10 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF204056"/>
+      <color rgb="FF8252DE"/>
       <color rgb="FFF20057"/>
       <color rgb="FFFFD636"/>
-      <color rgb="FF8252DE"/>
-      <color rgb="FF204056"/>
       <color rgb="FFFEF5F0"/>
       <color rgb="FFE7FFE7"/>
       <color rgb="FFFBFFFB"/>
@@ -2180,16 +2321,57 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15B86D8A-CBC0-49C9-9806-C0813A4AC871}">
-  <dimension ref="A4:M78"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="34.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="24.88671875" customWidth="1"/>
+    <col min="5" max="5" width="24.88671875" customWidth="1"/>
+    <col min="6" max="6" width="30.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" customWidth="1"/>
     <col min="10" max="10" width="36.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="52.5546875" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+    </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
@@ -2198,6 +2380,10 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
@@ -2205,8 +2391,14 @@
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
+      <c r="F5" s="24" t="s">
+        <v>136</v>
+      </c>
       <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
     </row>
     <row r="6" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2"/>
@@ -2217,9 +2409,15 @@
       <c r="D6" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="2"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="2"/>
     </row>
     <row r="7" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2"/>
@@ -2229,8 +2427,12 @@
         <v>2</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
+      <c r="F7" s="25"/>
       <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
       <c r="M7" t="s">
         <v>33</v>
       </c>
@@ -2239,12 +2441,16 @@
       <c r="A8" s="2"/>
       <c r="B8" s="3"/>
       <c r="C8" s="4"/>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="21" t="s">
         <v>3</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
     </row>
     <row r="9" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2"/>
@@ -2256,6 +2462,10 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
       <c r="M9" t="s">
         <v>34</v>
       </c>
@@ -2268,6 +2478,10 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
     </row>
     <row r="11" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2"/>
@@ -2277,6 +2491,10 @@
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
       <c r="M11" t="s">
         <v>35</v>
       </c>
@@ -2295,6 +2513,10 @@
         <v>7</v>
       </c>
       <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="2"/>
       <c r="M12" t="s">
         <v>36</v>
       </c>
@@ -2307,6 +2529,10 @@
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
     </row>
     <row r="14" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2"/>
@@ -2320,6 +2546,10 @@
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
       <c r="M14" t="s">
         <v>37</v>
       </c>
@@ -2334,6 +2564,10 @@
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
       <c r="M15" t="s">
         <v>38</v>
       </c>
@@ -2348,6 +2582,10 @@
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
       <c r="M16" t="s">
         <v>39</v>
       </c>
@@ -2362,17 +2600,25 @@
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
     </row>
     <row r="18" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="21" t="s">
         <v>8</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
       <c r="M18" t="s">
         <v>40</v>
       </c>
@@ -2387,6 +2633,10 @@
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
       <c r="M19" t="s">
         <v>41</v>
       </c>
@@ -2399,10 +2649,14 @@
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="21" t="s">
         <v>27</v>
       </c>
       <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
       <c r="M20" t="s">
         <v>42</v>
       </c>
@@ -2417,17 +2671,25 @@
       </c>
       <c r="F21" s="4"/>
       <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
     </row>
     <row r="22" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2"/>
       <c r="B22" s="3"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="21" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="4"/>
       <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
       <c r="M22" t="s">
         <v>43</v>
       </c>
@@ -2442,6 +2704,10 @@
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
       <c r="M23" t="s">
         <v>44</v>
       </c>
@@ -2456,6 +2722,10 @@
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
     </row>
     <row r="25" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
@@ -2467,6 +2737,10 @@
       </c>
       <c r="F25" s="4"/>
       <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
       <c r="M25" t="s">
         <v>45</v>
       </c>
@@ -2483,6 +2757,10 @@
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
       <c r="M26" t="s">
         <v>46</v>
       </c>
@@ -2497,6 +2775,10 @@
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
     </row>
     <row r="28" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
@@ -2506,6 +2788,10 @@
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
       <c r="M28" t="s">
         <v>47</v>
       </c>
@@ -2520,6 +2806,10 @@
         <v>25</v>
       </c>
       <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
       <c r="M29" t="s">
         <v>48</v>
       </c>
@@ -2534,6 +2824,10 @@
         <v>28</v>
       </c>
       <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
     </row>
     <row r="31" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
@@ -2545,6 +2839,10 @@
         <v>26</v>
       </c>
       <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
       <c r="M31" t="s">
         <v>49</v>
       </c>
@@ -2559,6 +2857,10 @@
       </c>
       <c r="F32" s="4"/>
       <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
       <c r="M32" t="s">
         <v>50</v>
       </c>
@@ -2568,11 +2870,15 @@
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="21" t="s">
         <v>22</v>
       </c>
       <c r="F33" s="4"/>
       <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
       <c r="M33" t="s">
         <v>51</v>
       </c>
@@ -2587,6 +2893,10 @@
       </c>
       <c r="F34" s="4"/>
       <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
     </row>
     <row r="35" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
@@ -2598,6 +2908,10 @@
       </c>
       <c r="F35" s="4"/>
       <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
       <c r="M35" t="s">
         <v>52</v>
       </c>
@@ -2612,6 +2926,10 @@
       </c>
       <c r="F36" s="4"/>
       <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
       <c r="M36" t="s">
         <v>53</v>
       </c>
@@ -2624,6 +2942,10 @@
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
       <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="2"/>
@@ -2633,18 +2955,51 @@
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="2"/>
       <c r="M38" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="2"/>
       <c r="M39" t="s">
         <v>55</v>
       </c>
     </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="2"/>
+    </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
       <c r="I41" s="4"/>
       <c r="J41" s="4"/>
+      <c r="K41" s="2"/>
       <c r="M41" t="s">
         <v>56</v>
       </c>
@@ -2659,6 +3014,7 @@
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
       <c r="M42" t="s">
         <v>57</v>
       </c>
@@ -2668,11 +3024,14 @@
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
+      <c r="F43" s="24" t="s">
+        <v>136</v>
+      </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
     </row>
     <row r="44" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
@@ -2682,14 +3041,17 @@
       <c r="D44" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="2"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="G44" s="23"/>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
       <c r="J44" s="4" t="s">
         <v>79</v>
       </c>
+      <c r="K44" s="2"/>
       <c r="M44" t="s">
         <v>58</v>
       </c>
@@ -2700,13 +3062,17 @@
       <c r="D45" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E45" s="4"/>
-      <c r="G45" s="2"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="G45" s="23"/>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
       <c r="J45" s="4" t="s">
         <v>80</v>
       </c>
+      <c r="K45" s="2"/>
       <c r="M45" t="s">
         <v>59</v>
       </c>
@@ -2717,14 +3083,17 @@
       <c r="D46" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="2"/>
+      <c r="E46" s="22"/>
+      <c r="F46" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="G46" s="23"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
       <c r="J46" s="4" t="s">
         <v>124</v>
       </c>
+      <c r="K46" s="2"/>
     </row>
     <row r="47" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B47" s="3"/>
@@ -2732,13 +3101,16 @@
       <c r="D47" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="F47" s="4"/>
-      <c r="G47" s="2"/>
+      <c r="F47" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="G47" s="23"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
       <c r="J47" s="4" t="s">
         <v>81</v>
       </c>
+      <c r="K47" s="2"/>
       <c r="M47" t="s">
         <v>60</v>
       </c>
@@ -2747,14 +3119,17 @@
       <c r="B48" s="3"/>
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="2"/>
+      <c r="E48" s="22"/>
+      <c r="F48" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="G48" s="23"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
       <c r="J48" s="4" t="s">
         <v>125</v>
       </c>
+      <c r="K48" s="2"/>
       <c r="M48" t="s">
         <v>61</v>
       </c>
@@ -2763,356 +3138,374 @@
       <c r="B49" s="3"/>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="2"/>
+      <c r="E49" s="22"/>
+      <c r="F49" s="25"/>
+      <c r="G49" s="23"/>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
-      <c r="J49" s="4" t="s">
-        <v>82</v>
-      </c>
+      <c r="J49" s="4"/>
+      <c r="K49" s="2"/>
     </row>
     <row r="50" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B50" s="3"/>
       <c r="C50" s="4"/>
-      <c r="D50" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G50" s="5"/>
-      <c r="H50" s="5"/>
-      <c r="I50" s="5"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="25"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
       <c r="J50" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="M50" t="s">
-        <v>62</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="K50" s="2"/>
     </row>
     <row r="51" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B51" s="3"/>
       <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
+      <c r="D51" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5"/>
       <c r="J51" s="4" t="s">
-        <v>83</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="K51" s="2"/>
       <c r="M51" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="52" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B52" s="3" t="s">
-        <v>5</v>
-      </c>
+      <c r="B52" s="3"/>
       <c r="C52" s="4"/>
-      <c r="D52" s="7" t="s">
-        <v>109</v>
-      </c>
+      <c r="D52" s="4"/>
       <c r="E52" s="4"/>
-      <c r="F52" s="8" t="s">
-        <v>91</v>
-      </c>
+      <c r="F52" s="4"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
       <c r="J52" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
+      </c>
+      <c r="K52" s="2"/>
+      <c r="M52" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="53" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B53" s="3"/>
+      <c r="B53" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="C53" s="4"/>
       <c r="D53" s="7" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
+      <c r="F53" s="8" t="s">
+        <v>91</v>
+      </c>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
       <c r="J53" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="M53" t="s">
-        <v>64</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="K53" s="2"/>
     </row>
     <row r="54" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B54" s="3"/>
       <c r="C54" s="4"/>
-      <c r="D54" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>93</v>
-      </c>
+      <c r="D54" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E54" s="4"/>
       <c r="F54" s="4"/>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
       <c r="J54" s="4" t="s">
-        <v>86</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="K54" s="2"/>
       <c r="M54" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="55" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B55" s="3"/>
       <c r="C55" s="4"/>
+      <c r="D55" s="4" t="s">
+        <v>94</v>
+      </c>
       <c r="E55" s="7" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
       <c r="J55" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B56" s="4"/>
+        <v>86</v>
+      </c>
+      <c r="K55" s="2"/>
+      <c r="M55" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="56" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B56" s="3"/>
       <c r="C56" s="4"/>
-      <c r="D56" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>101</v>
+      <c r="E56" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
       <c r="I56" s="2"/>
       <c r="J56" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="M56" t="s">
-        <v>66</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="K56" s="2"/>
     </row>
     <row r="57" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
       <c r="D57" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="E57" s="4"/>
-      <c r="F57" s="8" t="s">
-        <v>105</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F57" s="4"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
       <c r="J57" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="58" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B58" s="3"/>
+        <v>127</v>
+      </c>
+      <c r="K57" s="2"/>
+      <c r="M57" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="58" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B58" s="4"/>
       <c r="C58" s="4"/>
-      <c r="D58" s="7" t="s">
-        <v>96</v>
+      <c r="D58" s="4" t="s">
+        <v>99</v>
       </c>
       <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
+      <c r="F58" s="8" t="s">
+        <v>105</v>
+      </c>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
       <c r="J58" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="M58" t="s">
-        <v>67</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="K58" s="2"/>
     </row>
     <row r="59" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B59" s="6" t="s">
-        <v>13</v>
-      </c>
+      <c r="B59" s="3"/>
       <c r="C59" s="4"/>
       <c r="D59" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E59" s="4"/>
-      <c r="F59" s="10" t="s">
-        <v>27</v>
-      </c>
+      <c r="F59" s="4"/>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
       <c r="J59" s="4" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B60" s="4"/>
+        <v>129</v>
+      </c>
+      <c r="K59" s="2"/>
+      <c r="M59" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="60" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B60" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="C60" s="4"/>
-      <c r="D60" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="F60" s="4"/>
+      <c r="D60" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E60" s="4"/>
+      <c r="F60" s="10" t="s">
+        <v>27</v>
+      </c>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
       <c r="J60" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="M60" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="61" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B61" s="3"/>
+        <v>130</v>
+      </c>
+      <c r="K60" s="2"/>
+    </row>
+    <row r="61" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B61" s="4"/>
       <c r="C61" s="4"/>
-      <c r="D61" s="4"/>
-      <c r="E61" s="4" t="s">
-        <v>102</v>
+      <c r="D61" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="F61" s="4"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
       <c r="J61" s="4" t="s">
-        <v>132</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="K61" s="2"/>
       <c r="M61" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="62" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B62" s="3"/>
       <c r="C62" s="4"/>
       <c r="D62" s="4"/>
-      <c r="E62" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F62" s="9"/>
+      <c r="E62" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F62" s="4"/>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
       <c r="J62" s="4" t="s">
-        <v>88</v>
+        <v>132</v>
+      </c>
+      <c r="K62" s="2"/>
+      <c r="M62" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="63" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B63" s="3"/>
       <c r="C63" s="4"/>
-      <c r="D63" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F63" s="9"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
       <c r="J63" s="4" t="s">
-        <v>89</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="K63" s="2"/>
     </row>
     <row r="64" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B64" s="3"/>
       <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
+      <c r="D64" s="10" t="s">
+        <v>9</v>
+      </c>
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
       <c r="J64" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="K64" s="2"/>
+    </row>
+    <row r="65" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B65" s="3"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+      <c r="J65" s="4" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E65" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="F65" s="4"/>
-      <c r="G65" s="2"/>
-      <c r="I65" s="2"/>
-      <c r="M65" t="s">
-        <v>70</v>
-      </c>
+      <c r="K65" s="2"/>
     </row>
     <row r="66" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
-      <c r="D66" s="4" t="s">
-        <v>104</v>
+      <c r="D66" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F66" s="4"/>
       <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
       <c r="I66" s="2"/>
-      <c r="J66" s="2"/>
+      <c r="K66" s="2"/>
       <c r="M66" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="67" spans="2:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="B67" s="3" t="s">
-        <v>18</v>
-      </c>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B67" s="4"/>
       <c r="C67" s="4"/>
-      <c r="D67" s="4"/>
-      <c r="E67" s="10" t="s">
-        <v>21</v>
+      <c r="D67" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>106</v>
       </c>
       <c r="F67" s="4"/>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B68" s="4"/>
+      <c r="K67" s="2"/>
+      <c r="M67" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="68" spans="2:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B68" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
       <c r="E68" s="10" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F68" s="4"/>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
-      <c r="M68" t="s">
-        <v>72</v>
-      </c>
+      <c r="K68" s="2"/>
     </row>
     <row r="69" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
+      <c r="E69" s="10" t="s">
+        <v>30</v>
+      </c>
       <c r="F69" s="4"/>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
+      <c r="K69" s="2"/>
       <c r="M69" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="70" spans="2:13" x14ac:dyDescent="0.3">
@@ -3120,13 +3513,15 @@
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
-      <c r="F70" s="10" t="s">
-        <v>25</v>
-      </c>
+      <c r="F70" s="4"/>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
+      <c r="K70" s="2"/>
+      <c r="M70" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="71" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B71" s="4"/>
@@ -3134,116 +3529,138 @@
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
       <c r="F71" s="10" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
-      <c r="M71" t="s">
-        <v>74</v>
-      </c>
+      <c r="K71" s="2"/>
     </row>
     <row r="72" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
-      <c r="F72" s="7" t="s">
-        <v>108</v>
+      <c r="F72" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
+      <c r="K72" s="2"/>
       <c r="M72" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="73" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
-      <c r="E73" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F73" s="4"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="7" t="s">
+        <v>108</v>
+      </c>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
+      <c r="K73" s="2"/>
+      <c r="M73" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="74" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
       <c r="E74" s="10" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F74" s="4"/>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
-      <c r="M74" t="s">
-        <v>76</v>
-      </c>
+      <c r="K74" s="2"/>
     </row>
     <row r="75" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
-      <c r="E75" s="11" t="s">
-        <v>24</v>
+      <c r="E75" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="F75" s="4"/>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
+      <c r="K75" s="2"/>
       <c r="M75" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="76" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
-      <c r="E76" s="10" t="s">
-        <v>29</v>
+      <c r="E76" s="11" t="s">
+        <v>24</v>
       </c>
       <c r="F76" s="4"/>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
       <c r="I76" s="2"/>
       <c r="J76" s="2"/>
+      <c r="K76" s="2"/>
+      <c r="M76" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="77" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
       <c r="E77" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F77" s="4"/>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
       <c r="I77" s="2"/>
       <c r="J77" s="2"/>
-      <c r="M77" t="s">
-        <v>78</v>
-      </c>
+      <c r="K77" s="2"/>
     </row>
     <row r="78" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
+      <c r="E78" s="10" t="s">
+        <v>31</v>
+      </c>
       <c r="F78" s="4"/>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
       <c r="I78" s="2"/>
       <c r="J78" s="2"/>
+      <c r="K78" s="2"/>
+      <c r="M78" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B79" s="4"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+      <c r="I79" s="2"/>
+      <c r="J79" s="2"/>
+      <c r="K79" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
